--- a/Gestion/DASHBOARD/Dashboard_MAHD_[Track_and_Logic] (1).xlsx
+++ b/Gestion/DASHBOARD/Dashboard_MAHD_[Track_and_Logic] (1).xlsx
@@ -105,7 +105,7 @@
         <color rgb="FF1155CC"/>
         <u/>
       </rPr>
-      <t>https://drive.google.com/drive/u/1/folders/16SrWn1pLvenryTY4D2ruQ_lnDCoEQh7_</t>
+      <t>https://github.com/SamuelLopez2410/CDIO3_Eq06_TrackLogic/tree/main/Gestion/REQUISITOS</t>
     </r>
     <r>
       <rPr>
@@ -336,7 +336,7 @@
         <color rgb="FF1155CC"/>
         <u/>
       </rPr>
-      <t>https://github.com/SamuelLopez2410/CDIO3_Eq06_TrackLogic/blob/main/Protocolo%20de%20pruebas/Plantilla%20de%20Protocolos%20de%20Prueba.xlsx</t>
+      <t>https://github.com/SamuelLopez2410/CDIO3_Eq06_TrackLogic/blob/main/Gestion/PROTOCOLO%20PRUEBA%20INDUSTRIAL/Plantilla%20de%20Protocolos%20de%20Prueba.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -392,12 +392,11 @@
         <color rgb="FF1155CC"/>
         <u/>
       </rPr>
-      <t>https://github.com/SamuelLopez2410/CDIO3_Eq06_TrackLogic/tree/main/02_Hardware</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <color rgb="FF1F1F1F"/>
+      <t>https://github.com/SamuelLopez2410/CDIO3_Eq06_TrackLogic/tree/main/Hardware</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -443,7 +442,20 @@
     </r>
   </si>
   <si>
-    <t>[Link a Lecciones]</t>
+    <r>
+      <rPr>
+        <i/>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://github.com/SamuelLopez2410/CDIO3_Eq06_TrackLogic/blob/main/Gestion/RETROSPECTIVA%20DEL%20IPAC/Retrospectiva_IPAC_TrackLogic.docx</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
   </si>
   <si>
     <r>
@@ -463,7 +475,20 @@
     </r>
   </si>
   <si>
-    <t>[Link al Portafolio]</t>
+    <r>
+      <rPr>
+        <i/>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://github.com/SamuelLopez2410/CDIO3_Eq06_TrackLogic</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
   </si>
   <si>
     <t>🔴 Riesgo Crítico (Nivel Novato)</t>
@@ -1243,7 +1268,7 @@
       </c>
       <c r="D11" s="8">
         <f>COUNTIF(D16:D30, TRUE)/COUNTA(C16:C30)</f>
-        <v>0.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1460,7 +1485,7 @@
         <v>30</v>
       </c>
       <c r="D26" s="19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E26" s="22" t="s">
         <v>31</v>
@@ -1504,9 +1529,9 @@
         <v>38</v>
       </c>
       <c r="D29" s="19" t="b">
-        <v>0</v>
-      </c>
-      <c r="E29" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="E29" s="20" t="s">
         <v>39</v>
       </c>
     </row>
@@ -1518,9 +1543,9 @@
         <v>40</v>
       </c>
       <c r="D30" s="19" t="b">
-        <v>0</v>
-      </c>
-      <c r="E30" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="E30" s="20" t="s">
         <v>41</v>
       </c>
     </row>
@@ -1560,14 +1585,16 @@
     <hyperlink r:id="rId8" ref="E25"/>
     <hyperlink r:id="rId9" ref="E27"/>
     <hyperlink r:id="rId10" location="gid=728356188" ref="E28"/>
+    <hyperlink r:id="rId11" ref="E29"/>
+    <hyperlink r:id="rId12" ref="E30"/>
   </hyperlinks>
   <printOptions gridLines="1" horizontalCentered="1"/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
   <pageSetup fitToHeight="0" paperSize="9" cellComments="atEnd" orientation="landscape" pageOrder="overThenDown"/>
-  <drawing r:id="rId11"/>
+  <drawing r:id="rId13"/>
   <tableParts count="2">
-    <tablePart r:id="rId14"/>
-    <tablePart r:id="rId15"/>
+    <tablePart r:id="rId16"/>
+    <tablePart r:id="rId17"/>
   </tableParts>
 </worksheet>
 </file>
